--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/o-higgins.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1562-19-CM26</t>
+          <t>2677-36-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>67506.00999999999</v>
+        <v>63261.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2677-36-CM26</t>
+          <t>1398-187-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>63261.21</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1398-187-CM26</t>
+          <t>1743-66-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>40809.78</v>
+        <v>405227.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1743-66-CM26</t>
+          <t>3598-440-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>405227.73</v>
+        <v>257242.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>598-17-CM26</t>
+          <t>1529-168-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>48768.71</v>
+        <v>19778.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3598-440-CM26</t>
+          <t>591-90-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>257242.59</v>
+        <v>913082.5600000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1529-168-CM26</t>
+          <t>591-86-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>19778.86</v>
+        <v>1718926.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>3954-31-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1718926.68</v>
+        <v>223123.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3954-31-CM26</t>
+          <t>591-293-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>223123.85</v>
+        <v>73717.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>591-293-CM26</t>
+          <t>3729-93-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,67 +2338,6 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>73717.23</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>3729-93-CM26</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>69.090.300-8</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>TCHILECOM</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
         <v>8273.450000000001</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/o-higgins.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/o-higgins.xlsx
@@ -562,7 +562,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1871,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1936,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2001,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2188,11 @@
           <t>76.516.485-0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2253,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2318,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/o-higgins.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/o-higgins.xlsx
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
